--- a/beni_data.xlsx
+++ b/beni_data.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="93">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="276" uniqueCount="180">
   <si>
     <t>Fecha</t>
   </si>
@@ -88,24 +88,12 @@
     <t>PREMIUM detectados</t>
   </si>
   <si>
-    <t>5 de marzo</t>
-  </si>
-  <si>
-    <t>6 de marzo</t>
-  </si>
-  <si>
-    <t>7 de marzo</t>
-  </si>
-  <si>
     <t>Prob BENI</t>
   </si>
   <si>
     <t>EDGE</t>
   </si>
   <si>
-    <t>4 de marzo</t>
-  </si>
-  <si>
     <t>Mexico</t>
   </si>
   <si>
@@ -115,27 +103,15 @@
     <t>2. Bundesliga</t>
   </si>
   <si>
-    <t>PERFIL BTTS</t>
-  </si>
-  <si>
     <t>Bundesliga</t>
   </si>
   <si>
     <t>1. Liga Polonia</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>8 de marzo</t>
-  </si>
-  <si>
     <t>3. Bundesliga</t>
   </si>
   <si>
-    <t>SUDAMERICAN BTTS</t>
-  </si>
-  <si>
     <t>Super Liga Serbia</t>
   </si>
   <si>
@@ -292,13 +268,298 @@
     <t>Verl</t>
   </si>
   <si>
-    <t>RESULTADO</t>
-  </si>
-  <si>
-    <t>YES</t>
-  </si>
-  <si>
-    <t>NO</t>
+    <t>Liga Eslovenia</t>
+  </si>
+  <si>
+    <t>WIN</t>
+  </si>
+  <si>
+    <t>Radomlje</t>
+  </si>
+  <si>
+    <t>Bravo</t>
+  </si>
+  <si>
+    <t>Almeria</t>
+  </si>
+  <si>
+    <t>Leonesa</t>
+  </si>
+  <si>
+    <t>Polonia Warzawa</t>
+  </si>
+  <si>
+    <t>Trabzonspor</t>
+  </si>
+  <si>
+    <t>LKS</t>
+  </si>
+  <si>
+    <t>Kayseri</t>
+  </si>
+  <si>
+    <t>Plock</t>
+  </si>
+  <si>
+    <t>Arka</t>
+  </si>
+  <si>
+    <t>Horsens</t>
+  </si>
+  <si>
+    <t>Lyngby</t>
+  </si>
+  <si>
+    <t>Espanyol</t>
+  </si>
+  <si>
+    <t>Oviedo</t>
+  </si>
+  <si>
+    <t>LaLiga</t>
+  </si>
+  <si>
+    <t>2da. Dinamarca</t>
+  </si>
+  <si>
+    <t>2da. Polonia</t>
+  </si>
+  <si>
+    <t>Turkish SuperLig</t>
+  </si>
+  <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
+    <t>Champions League</t>
+  </si>
+  <si>
+    <t>HT 1.5</t>
+  </si>
+  <si>
+    <t>Galatasaray</t>
+  </si>
+  <si>
+    <t>Liverpool</t>
+  </si>
+  <si>
+    <t>Bayern Munich</t>
+  </si>
+  <si>
+    <t>MK Dons</t>
+  </si>
+  <si>
+    <t>Atalanta</t>
+  </si>
+  <si>
+    <t>Atletico Madrid</t>
+  </si>
+  <si>
+    <t>Tottenham</t>
+  </si>
+  <si>
+    <t>Gillingham</t>
+  </si>
+  <si>
+    <t>Championship</t>
+  </si>
+  <si>
+    <t>Wrexham</t>
+  </si>
+  <si>
+    <t>Hull City</t>
+  </si>
+  <si>
+    <t>3. Inglaterra</t>
+  </si>
+  <si>
+    <t>Liga Argentina</t>
+  </si>
+  <si>
+    <t>Union Santa Fe</t>
+  </si>
+  <si>
+    <t>Velez Sarfield</t>
+  </si>
+  <si>
+    <t>Tigre</t>
+  </si>
+  <si>
+    <t>Independiente</t>
+  </si>
+  <si>
+    <t>Bodo/Glimt</t>
+  </si>
+  <si>
+    <t>Sporting CP</t>
+  </si>
+  <si>
+    <t>Europa League</t>
+  </si>
+  <si>
+    <t>Conference League</t>
+  </si>
+  <si>
+    <t>Damac</t>
+  </si>
+  <si>
+    <t>Al Najma</t>
+  </si>
+  <si>
+    <t>Sigma Omoluc</t>
+  </si>
+  <si>
+    <t>Mainz</t>
+  </si>
+  <si>
+    <t>Celta de Vigo</t>
+  </si>
+  <si>
+    <t>Rijeka</t>
+  </si>
+  <si>
+    <t>Strasburgo</t>
+  </si>
+  <si>
+    <t>Lyon</t>
+  </si>
+  <si>
+    <t>Neom</t>
+  </si>
+  <si>
+    <t>Al Taawoun</t>
+  </si>
+  <si>
+    <t>Saudi Pro League</t>
+  </si>
+  <si>
+    <t>Lech Poznan</t>
+  </si>
+  <si>
+    <t>Shakhtar</t>
+  </si>
+  <si>
+    <t>Liga Brasilera</t>
+  </si>
+  <si>
+    <t>Flamengo</t>
+  </si>
+  <si>
+    <t>River Plate</t>
+  </si>
+  <si>
+    <t>Huracan</t>
+  </si>
+  <si>
+    <t>Remo</t>
+  </si>
+  <si>
+    <t>Liga Croacia</t>
+  </si>
+  <si>
+    <t>Varazdin</t>
+  </si>
+  <si>
+    <t>Swensea</t>
+  </si>
+  <si>
+    <t>1 mitad</t>
+  </si>
+  <si>
+    <t>Vukovar 1991</t>
+  </si>
+  <si>
+    <t>2da. España</t>
+  </si>
+  <si>
+    <t>Ruch</t>
+  </si>
+  <si>
+    <t>Stal Mielec</t>
+  </si>
+  <si>
+    <t>Real Zaragoza</t>
+  </si>
+  <si>
+    <t>Ljubljana</t>
+  </si>
+  <si>
+    <t>Jagiellonia</t>
+  </si>
+  <si>
+    <t>Piast</t>
+  </si>
+  <si>
+    <t>Liga Colombia</t>
+  </si>
+  <si>
+    <t>Vitoria</t>
+  </si>
+  <si>
+    <t>Atletico Mineiro</t>
+  </si>
+  <si>
+    <t>Cucuta</t>
+  </si>
+  <si>
+    <t>Deportivo Cali</t>
+  </si>
+  <si>
+    <t>Real Betis</t>
+  </si>
+  <si>
+    <t>Fluminense</t>
+  </si>
+  <si>
+    <t>Athletico PR</t>
+  </si>
+  <si>
+    <t>Gimnasia la Plata</t>
+  </si>
+  <si>
+    <t>Rivadavia</t>
+  </si>
+  <si>
+    <t>Liga Francia</t>
+  </si>
+  <si>
+    <t>Rennes</t>
+  </si>
+  <si>
+    <t>Lille</t>
+  </si>
+  <si>
+    <t>Liga Serbia</t>
+  </si>
+  <si>
+    <t>Liga Rumania</t>
+  </si>
+  <si>
+    <t>Universidad Cluj</t>
+  </si>
+  <si>
+    <t>CFR Cluj</t>
+  </si>
+  <si>
+    <t>Barracas Central</t>
+  </si>
+  <si>
+    <t>Atletico Tucuman</t>
+  </si>
+  <si>
+    <t>OFK Beograd</t>
+  </si>
+  <si>
+    <t>Napredak</t>
+  </si>
+  <si>
+    <t>Gremio</t>
+  </si>
+  <si>
+    <t>Chapecoense</t>
+  </si>
+  <si>
+    <t>Instituto</t>
   </si>
 </sst>
 </file>
@@ -348,7 +609,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -417,12 +678,39 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
     <cellStyle name="Porcentaje" xfId="1" builtinId="5"/>
   </cellStyles>
-  <dxfs count="36">
+  <dxfs count="9">
     <dxf>
       <font>
         <b/>
@@ -438,50 +726,6 @@
       <fill>
         <patternFill>
           <bgColor rgb="FFC00000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor theme="6"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
         </patternFill>
       </fill>
     </dxf>
@@ -522,292 +766,6 @@
           <bgColor rgb="FFFF0000"/>
         </patternFill>
       </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF00B050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b val="0"/>
-        <i/>
-      </font>
-      <numFmt numFmtId="0" formatCode="General"/>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FF92D050"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFF0000"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-      </font>
-      <border>
-        <left style="thin">
-          <color auto="1"/>
-        </left>
-        <right style="thin">
-          <color auto="1"/>
-        </right>
-        <top style="thin">
-          <color auto="1"/>
-        </top>
-        <bottom style="thin">
-          <color auto="1"/>
-        </bottom>
-        <vertical/>
-        <horizontal/>
-      </border>
     </dxf>
     <dxf>
       <font>
@@ -1146,17 +1104,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:V38"/>
+  <dimension ref="A1:V66"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="18" style="7" customWidth="1"/>
+    <col min="1" max="1" width="18" style="27" customWidth="1"/>
     <col min="2" max="2" width="22.5703125" style="7" customWidth="1"/>
-    <col min="3" max="3" width="19.140625" style="7" customWidth="1"/>
+    <col min="3" max="3" width="21" style="7" customWidth="1"/>
     <col min="4" max="4" width="25.42578125" style="7" customWidth="1"/>
     <col min="5" max="5" width="18" style="7" customWidth="1"/>
     <col min="6" max="6" width="12.42578125" style="7" customWidth="1"/>
-    <col min="7" max="7" width="12.85546875" style="7" customWidth="1"/>
-    <col min="8" max="8" width="12.140625" style="7" customWidth="1"/>
+    <col min="7" max="7" width="14" style="29" customWidth="1"/>
+    <col min="8" max="8" width="13.5703125" style="29" customWidth="1"/>
     <col min="9" max="9" width="11.85546875" style="13" customWidth="1"/>
     <col min="10" max="10" width="11.5703125" style="13" customWidth="1"/>
     <col min="11" max="11" width="13.85546875" style="13" customWidth="1"/>
@@ -1175,17 +1133,17 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>39</v>
+        <v>31</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>2</v>
@@ -1193,10 +1151,10 @@
       <c r="F1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="28" t="s">
         <v>5</v>
       </c>
       <c r="I1" s="6" t="s">
@@ -1212,10 +1170,10 @@
         <v>9</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>78</v>
+        <v>70</v>
       </c>
       <c r="N1" s="8" t="s">
-        <v>79</v>
+        <v>71</v>
       </c>
       <c r="O1" s="6" t="s">
         <v>10</v>
@@ -1224,32 +1182,28 @@
         <v>11</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="R1" s="8" t="s">
-        <v>26</v>
-      </c>
-      <c r="S1" s="17" t="s">
-        <v>31</v>
-      </c>
-      <c r="T1" s="2" t="s">
-        <v>90</v>
-      </c>
+        <v>23</v>
+      </c>
+      <c r="S1" s="17"/>
+      <c r="T1" s="2"/>
       <c r="U1" s="21"/>
       <c r="V1" s="5"/>
     </row>
     <row r="2" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
-        <v>27</v>
+      <c r="A2" s="27">
+        <v>46085</v>
       </c>
       <c r="B2" s="7" t="s">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="D2" s="7" t="s">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="E2" s="7" t="s">
         <v>13</v>
@@ -1257,10 +1211,10 @@
       <c r="F2" s="7">
         <v>1.42</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="29">
         <v>2</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="29">
         <v>1</v>
       </c>
       <c r="I2" s="10">
@@ -1296,30 +1250,22 @@
         <f t="shared" ref="R2:R17" si="2">Q2-P2</f>
         <v>4.5774647887323883E-2</v>
       </c>
-      <c r="S2" s="20" t="str">
-        <f>IF(AND(OR(M2&gt;=75%,(M2+N2)/2&gt;=75%),N2&gt;=75%,K2&gt;=1.5,L2&gt;=1.5,O2&gt;=3.6),"SUPER BTTS",
-IF(AND(OR(M2&gt;=70%,(M2+N2)/2&gt;=70%),N2&gt;=70%,K2&gt;=1.4,L2&gt;=1.4,O2&gt;=3.2),"PREMIUM BTTS",
-IF(AND(OR(M2&gt;=63%,(M2+N2)/2&gt;=63%),N2&gt;=63%,K2&gt;=1.3,L2&gt;=1.3,O2&gt;=3),"S+ BTTS","")))</f>
-        <v>S+ BTTS</v>
-      </c>
-      <c r="T2" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="S2" s="20"/>
       <c r="U2" s="12"/>
       <c r="V2" s="12"/>
     </row>
     <row r="3" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
-        <v>27</v>
+      <c r="A3" s="27">
+        <v>46085</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>43</v>
+        <v>35</v>
       </c>
       <c r="D3" s="7" t="s">
-        <v>60</v>
+        <v>52</v>
       </c>
       <c r="E3" s="7" t="s">
         <v>13</v>
@@ -1327,10 +1273,10 @@
       <c r="F3" s="7">
         <v>1.7</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="29">
         <v>2</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="29">
         <v>1</v>
       </c>
       <c r="I3" s="10">
@@ -1366,27 +1312,22 @@
         <f t="shared" si="2"/>
         <v>4.1764705882352926E-2</v>
       </c>
-      <c r="S3" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="T3" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="S3" s="20"/>
       <c r="U3" s="12"/>
       <c r="V3" s="12"/>
     </row>
     <row r="4" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
-        <v>27</v>
+      <c r="A4" s="27">
+        <v>46085</v>
       </c>
       <c r="B4" s="7" t="s">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="D4" s="7" t="s">
-        <v>59</v>
+        <v>51</v>
       </c>
       <c r="E4" s="7" t="s">
         <v>13</v>
@@ -1394,10 +1335,10 @@
       <c r="F4" s="7">
         <v>1.7</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="29">
         <v>3</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="29">
         <v>1</v>
       </c>
       <c r="I4" s="13">
@@ -1433,27 +1374,22 @@
         <f t="shared" si="2"/>
         <v>7.1764705882352953E-2</v>
       </c>
-      <c r="S4" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="T4" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="S4" s="3"/>
       <c r="U4" s="12"/>
       <c r="V4" s="12"/>
     </row>
     <row r="5" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A5" s="7" t="s">
-        <v>22</v>
+      <c r="A5" s="27">
+        <v>46086</v>
       </c>
       <c r="B5" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>58</v>
+        <v>50</v>
       </c>
       <c r="E5" s="7" t="s">
         <v>13</v>
@@ -1461,10 +1397,10 @@
       <c r="F5" s="7">
         <v>1.42</v>
       </c>
-      <c r="G5" s="7">
+      <c r="G5" s="29">
         <v>2</v>
       </c>
-      <c r="H5" s="7">
+      <c r="H5" s="29">
         <v>2</v>
       </c>
       <c r="I5" s="13">
@@ -1500,30 +1436,22 @@
         <f t="shared" si="2"/>
         <v>4.5774647887323883E-2</v>
       </c>
-      <c r="S5" s="20" t="str">
-        <f t="shared" ref="S5:S15" si="5">IF(AND(OR(M5&gt;=75%,(M5+N5)/2&gt;=75%),N5&gt;=75%,K5&gt;=1.5,L5&gt;=1.5,O5&gt;=3.6),"SUPER BTTS",
-IF(AND(OR(M5&gt;=70%,(M5+N5)/2&gt;=70%),N5&gt;=70%,K5&gt;=1.4,L5&gt;=1.4,O5&gt;=3.2),"PREMIUM BTTS",
-IF(AND(OR(M5&gt;=63%,(M5+N5)/2&gt;=63%),N5&gt;=63%,K5&gt;=1.3,L5&gt;=1.3,O5&gt;=3),"S+ BTTS","")))</f>
-        <v>S+ BTTS</v>
-      </c>
-      <c r="T5" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="S5" s="20"/>
       <c r="U5" s="12"/>
       <c r="V5" s="12"/>
     </row>
     <row r="6" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A6" s="7" t="s">
-        <v>23</v>
+      <c r="A6" s="27">
+        <v>46087</v>
       </c>
       <c r="B6" s="7" t="s">
         <v>14</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>13</v>
@@ -1531,10 +1459,10 @@
       <c r="F6" s="7">
         <v>1.61</v>
       </c>
-      <c r="G6" s="7">
+      <c r="G6" s="29">
         <v>0</v>
       </c>
-      <c r="H6" s="7">
+      <c r="H6" s="29">
         <v>1</v>
       </c>
       <c r="I6" s="10">
@@ -1570,28 +1498,22 @@
         <f t="shared" si="2"/>
         <v>7.8881987577639756E-2</v>
       </c>
-      <c r="S6" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>S+ BTTS</v>
-      </c>
-      <c r="T6" s="7" t="s">
-        <v>92</v>
-      </c>
+      <c r="S6" s="20"/>
       <c r="U6" s="12"/>
       <c r="V6" s="12"/>
     </row>
     <row r="7" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A7" s="7" t="s">
-        <v>23</v>
+      <c r="A7" s="27">
+        <v>46087</v>
       </c>
       <c r="B7" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="D7" s="7" t="s">
-        <v>56</v>
+        <v>48</v>
       </c>
       <c r="E7" s="7" t="s">
         <v>13</v>
@@ -1599,10 +1521,10 @@
       <c r="F7" s="7">
         <v>1.66</v>
       </c>
-      <c r="G7" s="7">
+      <c r="G7" s="29">
         <v>0</v>
       </c>
-      <c r="H7" s="7">
+      <c r="H7" s="29">
         <v>0</v>
       </c>
       <c r="I7" s="10">
@@ -1638,27 +1560,21 @@
         <f t="shared" si="2"/>
         <v>9.7590361445783036E-2</v>
       </c>
-      <c r="S7" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>PREMIUM BTTS</v>
-      </c>
-      <c r="T7" s="7" t="s">
-        <v>92</v>
-      </c>
+      <c r="S7" s="20"/>
       <c r="U7" s="12"/>
     </row>
     <row r="8" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A8" s="7" t="s">
-        <v>23</v>
+      <c r="A8" s="27">
+        <v>46087</v>
       </c>
       <c r="B8" s="7" t="s">
         <v>16</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>55</v>
+        <v>47</v>
       </c>
       <c r="E8" s="7" t="s">
         <v>13</v>
@@ -1666,10 +1582,10 @@
       <c r="F8" s="7">
         <v>1.42</v>
       </c>
-      <c r="G8" s="7">
+      <c r="G8" s="29">
         <v>0</v>
       </c>
-      <c r="H8" s="7">
+      <c r="H8" s="29">
         <v>2</v>
       </c>
       <c r="I8" s="10">
@@ -1705,27 +1621,21 @@
         <f t="shared" si="2"/>
         <v>4.5774647887323883E-2</v>
       </c>
-      <c r="S8" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>PREMIUM BTTS</v>
-      </c>
-      <c r="T8" s="7" t="s">
-        <v>92</v>
-      </c>
+      <c r="S8" s="20"/>
       <c r="U8" s="12"/>
     </row>
     <row r="9" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A9" s="7" t="s">
-        <v>24</v>
+      <c r="A9" s="27">
+        <v>46088</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>53</v>
+        <v>45</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>54</v>
+        <v>46</v>
       </c>
       <c r="E9" s="7" t="s">
         <v>13</v>
@@ -1733,10 +1643,10 @@
       <c r="F9" s="9">
         <v>1.55</v>
       </c>
-      <c r="G9" s="7">
+      <c r="G9" s="29">
         <v>0</v>
       </c>
-      <c r="H9" s="7">
+      <c r="H9" s="29">
         <v>1</v>
       </c>
       <c r="I9" s="9">
@@ -1772,27 +1682,21 @@
         <f t="shared" si="2"/>
         <v>5.4838709677419328E-2</v>
       </c>
-      <c r="S9" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>S+ BTTS</v>
-      </c>
-      <c r="T9" s="7" t="s">
-        <v>92</v>
-      </c>
+      <c r="S9" s="20"/>
       <c r="U9" s="12"/>
     </row>
     <row r="10" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A10" s="7" t="s">
-        <v>24</v>
+      <c r="A10" s="27">
+        <v>46088</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="D10" s="7" t="s">
-        <v>61</v>
+        <v>53</v>
       </c>
       <c r="E10" s="7" t="s">
         <v>13</v>
@@ -1800,10 +1704,10 @@
       <c r="F10" s="7">
         <v>1.75</v>
       </c>
-      <c r="G10" s="7">
-        <v>1</v>
-      </c>
-      <c r="H10" s="7">
+      <c r="G10" s="29">
+        <v>1</v>
+      </c>
+      <c r="H10" s="29">
         <v>1</v>
       </c>
       <c r="I10" s="13">
@@ -1839,27 +1743,21 @@
         <f t="shared" si="2"/>
         <v>7.8571428571428625E-2</v>
       </c>
-      <c r="S10" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>S+ BTTS</v>
-      </c>
-      <c r="T10" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="S10" s="20"/>
       <c r="U10" s="12"/>
     </row>
     <row r="11" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A11" s="7" t="s">
-        <v>24</v>
+      <c r="A11" s="27">
+        <v>46088</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>30</v>
+        <v>26</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>63</v>
+        <v>55</v>
       </c>
       <c r="D11" s="7" t="s">
-        <v>62</v>
+        <v>54</v>
       </c>
       <c r="E11" s="7" t="s">
         <v>13</v>
@@ -1867,10 +1765,10 @@
       <c r="F11" s="9">
         <v>1.44</v>
       </c>
-      <c r="G11" s="9">
+      <c r="G11" s="30">
         <v>2</v>
       </c>
-      <c r="H11" s="9">
+      <c r="H11" s="30">
         <v>4</v>
       </c>
       <c r="I11" s="10">
@@ -1906,27 +1804,21 @@
         <f t="shared" si="2"/>
         <v>5.555555555555558E-2</v>
       </c>
-      <c r="S11" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>PREMIUM BTTS</v>
-      </c>
-      <c r="T11" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="S11" s="20"/>
       <c r="U11" s="12"/>
     </row>
     <row r="12" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A12" s="7" t="s">
-        <v>24</v>
+      <c r="A12" s="27">
+        <v>46088</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>68</v>
+        <v>60</v>
       </c>
       <c r="E12" s="7" t="s">
         <v>13</v>
@@ -1934,10 +1826,10 @@
       <c r="F12" s="9">
         <v>1.55</v>
       </c>
-      <c r="G12" s="9">
-        <v>1</v>
-      </c>
-      <c r="H12" s="9">
+      <c r="G12" s="30">
+        <v>1</v>
+      </c>
+      <c r="H12" s="30">
         <v>2</v>
       </c>
       <c r="I12" s="10">
@@ -1973,27 +1865,21 @@
         <f t="shared" si="2"/>
         <v>7.4838709677419346E-2</v>
       </c>
-      <c r="S12" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>S+ BTTS</v>
-      </c>
-      <c r="T12" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="S12" s="20"/>
       <c r="U12" s="12"/>
     </row>
     <row r="13" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A13" s="7" t="s">
-        <v>24</v>
+      <c r="A13" s="27">
+        <v>46088</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>82</v>
+        <v>74</v>
       </c>
       <c r="E13" s="7" t="s">
         <v>13</v>
@@ -2001,10 +1887,10 @@
       <c r="F13" s="9">
         <v>1.57</v>
       </c>
-      <c r="G13" s="9">
+      <c r="G13" s="30">
         <v>2</v>
       </c>
-      <c r="H13" s="7">
+      <c r="H13" s="29">
         <v>1</v>
       </c>
       <c r="I13" s="10">
@@ -2040,27 +1926,21 @@
         <f t="shared" si="2"/>
         <v>4.305732484076441E-2</v>
       </c>
-      <c r="S13" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>S+ BTTS</v>
-      </c>
-      <c r="T13" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="S13" s="20"/>
       <c r="U13" s="12"/>
     </row>
     <row r="14" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A14" s="7" t="s">
-        <v>24</v>
+      <c r="A14" s="27">
+        <v>46088</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="D14" s="3" t="s">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="E14" s="7" t="s">
         <v>13</v>
@@ -2068,10 +1948,10 @@
       <c r="F14" s="9">
         <v>1.57</v>
       </c>
-      <c r="G14" s="9">
+      <c r="G14" s="30">
         <v>3</v>
       </c>
-      <c r="H14" s="9">
+      <c r="H14" s="30">
         <v>0</v>
       </c>
       <c r="I14" s="10">
@@ -2107,27 +1987,21 @@
         <f t="shared" si="2"/>
         <v>3.3057324840764402E-2</v>
       </c>
-      <c r="S14" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>S+ BTTS</v>
-      </c>
-      <c r="T14" s="7" t="s">
-        <v>92</v>
-      </c>
+      <c r="S14" s="20"/>
       <c r="U14" s="22"/>
     </row>
     <row r="15" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A15" s="7" t="s">
-        <v>24</v>
+      <c r="A15" s="27">
+        <v>46088</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>66</v>
+        <v>58</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>67</v>
+        <v>59</v>
       </c>
       <c r="E15" s="7" t="s">
         <v>13</v>
@@ -2135,10 +2009,10 @@
       <c r="F15" s="9">
         <v>1.42</v>
       </c>
-      <c r="G15" s="9">
+      <c r="G15" s="30">
         <v>2</v>
       </c>
-      <c r="H15" s="9">
+      <c r="H15" s="30">
         <v>1</v>
       </c>
       <c r="I15" s="10">
@@ -2174,27 +2048,21 @@
         <f t="shared" si="2"/>
         <v>3.5774647887323874E-2</v>
       </c>
-      <c r="S15" s="20" t="str">
-        <f t="shared" si="5"/>
-        <v>PREMIUM BTTS</v>
-      </c>
-      <c r="T15" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="S15" s="20"/>
       <c r="U15" s="12"/>
     </row>
     <row r="16" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A16" s="7" t="s">
+      <c r="A16" s="27">
+        <v>46088</v>
+      </c>
+      <c r="B16" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B16" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="C16" s="7" t="s">
-        <v>51</v>
+        <v>43</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E16" s="7" t="s">
         <v>13</v>
@@ -2202,10 +2070,10 @@
       <c r="F16" s="9">
         <v>1.83</v>
       </c>
-      <c r="G16" s="9">
-        <v>1</v>
-      </c>
-      <c r="H16" s="9">
+      <c r="G16" s="30">
+        <v>1</v>
+      </c>
+      <c r="H16" s="30">
         <v>2</v>
       </c>
       <c r="I16" s="10">
@@ -2231,7 +2099,7 @@
         <v>2.81</v>
       </c>
       <c r="P16" s="11">
-        <f t="shared" ref="P16:P22" si="6">1/F16</f>
+        <f t="shared" ref="P16:P22" si="5">1/F16</f>
         <v>0.54644808743169393</v>
       </c>
       <c r="Q16" s="4">
@@ -2241,27 +2109,22 @@
         <f t="shared" si="2"/>
         <v>9.3551912568306084E-2</v>
       </c>
-      <c r="S16" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="T16" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="S16" s="3"/>
       <c r="U16" s="23"/>
       <c r="V16" s="15"/>
     </row>
     <row r="17" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A17" s="7" t="s">
+      <c r="A17" s="27">
+        <v>46088</v>
+      </c>
+      <c r="B17" s="7" t="s">
         <v>24</v>
       </c>
-      <c r="B17" s="7" t="s">
-        <v>28</v>
-      </c>
       <c r="C17" s="7" t="s">
-        <v>69</v>
+        <v>61</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>84</v>
+        <v>76</v>
       </c>
       <c r="E17" s="7" t="s">
         <v>13</v>
@@ -2269,10 +2132,10 @@
       <c r="F17" s="9">
         <v>1.85</v>
       </c>
-      <c r="G17" s="9">
+      <c r="G17" s="30">
         <v>3</v>
       </c>
-      <c r="H17" s="9">
+      <c r="H17" s="30">
         <v>0</v>
       </c>
       <c r="I17" s="10">
@@ -2298,7 +2161,7 @@
         <v>3.4499999999999997</v>
       </c>
       <c r="P17" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.54054054054054046</v>
       </c>
       <c r="Q17" s="4">
@@ -2308,27 +2171,22 @@
         <f t="shared" si="2"/>
         <v>0.14945945945945949</v>
       </c>
-      <c r="S17" s="3" t="s">
-        <v>37</v>
-      </c>
-      <c r="T17" s="7" t="s">
-        <v>92</v>
-      </c>
+      <c r="S17" s="3"/>
       <c r="U17" s="23"/>
       <c r="V17" s="15"/>
     </row>
     <row r="18" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A18" s="7" t="s">
-        <v>35</v>
+      <c r="A18" s="27">
+        <v>46089</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>52</v>
+        <v>44</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>81</v>
+        <v>73</v>
       </c>
       <c r="E18" s="7" t="s">
         <v>13</v>
@@ -2336,10 +2194,10 @@
       <c r="F18" s="9">
         <v>1.53</v>
       </c>
-      <c r="G18" s="9">
+      <c r="G18" s="30">
         <v>3</v>
       </c>
-      <c r="H18" s="9">
+      <c r="H18" s="30">
         <v>1</v>
       </c>
       <c r="I18" s="10">
@@ -2361,43 +2219,35 @@
         <v>0.85</v>
       </c>
       <c r="O18" s="13">
-        <f t="shared" ref="O18:O24" si="7">I18+J18</f>
+        <f t="shared" ref="O18:O26" si="6">I18+J18</f>
         <v>3.0300000000000002</v>
       </c>
       <c r="P18" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.65359477124183007</v>
       </c>
       <c r="Q18" s="4">
         <v>0.7</v>
       </c>
       <c r="R18" s="11">
-        <f t="shared" ref="R18:R24" si="8">Q18-P18</f>
+        <f t="shared" ref="R18:R66" si="7">Q18-P18</f>
         <v>4.6405228758169881E-2</v>
       </c>
-      <c r="S18" s="18" t="str">
-        <f t="shared" ref="S18:S22" si="9">IF(AND(OR(M18&gt;=75%,(M18+N18)/2&gt;=75%),N18&gt;=75%,K18&gt;=1.5,L18&gt;=1.5,O18&gt;=3.6),"SUPER BTTS",
-IF(AND(OR(M18&gt;=70%,(M18+N18)/2&gt;=70%),N18&gt;=70%,K18&gt;=1.4,L18&gt;=1.4,O18&gt;=3.2),"PREMIUM BTTS",
-IF(AND(OR(M18&gt;=63%,(M18+N18)/2&gt;=63%),N18&gt;=63%,K18&gt;=1.3,L18&gt;=1.3,O18&gt;=3),"S+ BTTS","")))</f>
-        <v>S+ BTTS</v>
-      </c>
-      <c r="T18" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="S18" s="18"/>
       <c r="U18" s="23"/>
     </row>
     <row r="19" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A19" s="7" t="s">
-        <v>35</v>
+      <c r="A19" s="27">
+        <v>46089</v>
       </c>
       <c r="B19" s="7" t="s">
         <v>15</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>71</v>
+        <v>63</v>
       </c>
       <c r="E19" s="7" t="s">
         <v>13</v>
@@ -2405,10 +2255,10 @@
       <c r="F19" s="9">
         <v>1.53</v>
       </c>
-      <c r="G19" s="9">
-        <v>1</v>
-      </c>
-      <c r="H19" s="9">
+      <c r="G19" s="30">
+        <v>1</v>
+      </c>
+      <c r="H19" s="30">
         <v>4</v>
       </c>
       <c r="I19" s="10">
@@ -2430,41 +2280,35 @@
         <v>0.75</v>
       </c>
       <c r="O19" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>3.69</v>
       </c>
       <c r="P19" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.65359477124183007</v>
       </c>
       <c r="Q19" s="4">
         <v>0.72</v>
       </c>
       <c r="R19" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>6.6405228758169899E-2</v>
       </c>
-      <c r="S19" s="18" t="str">
-        <f t="shared" si="9"/>
-        <v>S+ BTTS</v>
-      </c>
-      <c r="T19" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="S19" s="18"/>
       <c r="U19" s="23"/>
     </row>
     <row r="20" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A20" s="7" t="s">
-        <v>35</v>
+      <c r="A20" s="27">
+        <v>46089</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>72</v>
+        <v>64</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>73</v>
+        <v>65</v>
       </c>
       <c r="E20" s="7" t="s">
         <v>13</v>
@@ -2472,10 +2316,10 @@
       <c r="F20" s="9">
         <v>1.62</v>
       </c>
-      <c r="G20" s="9">
+      <c r="G20" s="30">
         <v>4</v>
       </c>
-      <c r="H20" s="9">
+      <c r="H20" s="30">
         <v>2</v>
       </c>
       <c r="I20" s="10">
@@ -2497,41 +2341,35 @@
         <v>0.64</v>
       </c>
       <c r="O20" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>3.19</v>
       </c>
       <c r="P20" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.61728395061728392</v>
       </c>
       <c r="Q20" s="4">
         <v>0.7</v>
       </c>
       <c r="R20" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>8.2716049382716039E-2</v>
       </c>
-      <c r="S20" s="18" t="str">
-        <f t="shared" si="9"/>
-        <v>S+ BTTS</v>
-      </c>
-      <c r="T20" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="S20" s="18"/>
       <c r="U20" s="23"/>
     </row>
     <row r="21" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A21" s="7" t="s">
-        <v>35</v>
+      <c r="A21" s="27">
+        <v>46089</v>
       </c>
       <c r="B21" s="7" t="s">
         <v>12</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>75</v>
+        <v>67</v>
       </c>
       <c r="D21" s="7" t="s">
-        <v>74</v>
+        <v>66</v>
       </c>
       <c r="E21" s="7" t="s">
         <v>13</v>
@@ -2539,10 +2377,10 @@
       <c r="F21" s="7">
         <v>1.55</v>
       </c>
-      <c r="G21" s="7">
+      <c r="G21" s="29">
         <v>2</v>
       </c>
-      <c r="H21" s="7">
+      <c r="H21" s="29">
         <v>3</v>
       </c>
       <c r="I21" s="13">
@@ -2564,40 +2402,34 @@
         <v>0.71</v>
       </c>
       <c r="O21" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>3.07</v>
       </c>
       <c r="P21" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.64516129032258063</v>
       </c>
       <c r="Q21" s="4">
         <v>0.69</v>
       </c>
       <c r="R21" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>4.4838709677419319E-2</v>
       </c>
-      <c r="S21" s="18" t="str">
-        <f t="shared" si="9"/>
-        <v>S+ BTTS</v>
-      </c>
-      <c r="T21" s="7" t="s">
-        <v>91</v>
-      </c>
+      <c r="S21" s="18"/>
     </row>
     <row r="22" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A22" s="7" t="s">
-        <v>35</v>
+      <c r="A22" s="27">
+        <v>46089</v>
       </c>
       <c r="B22" s="7" t="s">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>77</v>
+        <v>69</v>
       </c>
       <c r="D22" s="7" t="s">
-        <v>76</v>
+        <v>68</v>
       </c>
       <c r="E22" s="7" t="s">
         <v>13</v>
@@ -2605,10 +2437,10 @@
       <c r="F22" s="7">
         <v>1.75</v>
       </c>
-      <c r="G22" s="7">
+      <c r="G22" s="29">
         <v>0</v>
       </c>
-      <c r="H22" s="7">
+      <c r="H22" s="29">
         <v>1</v>
       </c>
       <c r="I22" s="13">
@@ -2630,40 +2462,34 @@
         <v>0.75</v>
       </c>
       <c r="O22" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>2.66</v>
       </c>
       <c r="P22" s="11">
-        <f t="shared" si="6"/>
+        <f t="shared" si="5"/>
         <v>0.5714285714285714</v>
       </c>
       <c r="Q22" s="4">
         <v>0.7</v>
       </c>
       <c r="R22" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>0.12857142857142856</v>
       </c>
-      <c r="S22" s="18" t="str">
-        <f t="shared" si="9"/>
-        <v/>
-      </c>
-      <c r="T22" s="7" t="s">
-        <v>92</v>
-      </c>
+      <c r="S22" s="18"/>
     </row>
     <row r="23" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A23" s="7" t="s">
-        <v>35</v>
+      <c r="A23" s="27">
+        <v>46089</v>
       </c>
       <c r="B23" s="7" t="s">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>86</v>
+        <v>78</v>
       </c>
       <c r="D23" s="7" t="s">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="E23" s="7" t="s">
         <v>13</v>
@@ -2671,10 +2497,10 @@
       <c r="F23" s="7">
         <v>1.94</v>
       </c>
-      <c r="G23" s="7">
-        <v>1</v>
-      </c>
-      <c r="H23" s="7">
+      <c r="G23" s="29">
+        <v>1</v>
+      </c>
+      <c r="H23" s="29">
         <v>0</v>
       </c>
       <c r="I23" s="13">
@@ -2696,7 +2522,7 @@
         <v>0.42</v>
       </c>
       <c r="O23" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>3.08</v>
       </c>
       <c r="P23" s="11">
@@ -2707,26 +2533,23 @@
         <v>0.57999999999999996</v>
       </c>
       <c r="R23" s="11">
-        <f t="shared" si="8"/>
+        <f t="shared" si="7"/>
         <v>6.4536082474226708E-2</v>
       </c>
       <c r="S23" s="18"/>
-      <c r="T23" s="7" t="s">
-        <v>92</v>
-      </c>
     </row>
     <row r="24" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="A24" s="7" t="s">
-        <v>35</v>
+      <c r="A24" s="27">
+        <v>46089</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>88</v>
+        <v>80</v>
       </c>
       <c r="D24" s="7" t="s">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="E24" s="7" t="s">
         <v>13</v>
@@ -2734,10 +2557,10 @@
       <c r="F24" s="7">
         <v>1.4</v>
       </c>
-      <c r="G24" s="7">
-        <v>1</v>
-      </c>
-      <c r="H24" s="7">
+      <c r="G24" s="29">
+        <v>1</v>
+      </c>
+      <c r="H24" s="29">
         <v>2</v>
       </c>
       <c r="I24" s="13">
@@ -2759,70 +2582,2516 @@
         <v>0.79</v>
       </c>
       <c r="O24" s="13">
-        <f t="shared" si="7"/>
+        <f t="shared" si="6"/>
         <v>3.5700000000000003</v>
       </c>
       <c r="P24" s="11">
-        <f t="shared" ref="P24" si="10">1/F24</f>
+        <f t="shared" ref="P24:P30" si="8">1/F24</f>
         <v>0.7142857142857143</v>
       </c>
       <c r="Q24" s="4">
         <v>0.76</v>
       </c>
       <c r="R24" s="11">
+        <f t="shared" si="7"/>
+        <v>4.5714285714285707E-2</v>
+      </c>
+      <c r="S24" s="18"/>
+    </row>
+    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A25" s="27">
+        <v>46090</v>
+      </c>
+      <c r="B25" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C25" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D25" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="E25" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F25" s="7">
+        <v>1.55</v>
+      </c>
+      <c r="G25" s="29">
+        <v>1</v>
+      </c>
+      <c r="H25" s="29">
+        <v>3</v>
+      </c>
+      <c r="I25" s="13">
+        <v>1.52</v>
+      </c>
+      <c r="J25" s="13">
+        <v>1.71</v>
+      </c>
+      <c r="K25" s="13">
+        <v>1.43</v>
+      </c>
+      <c r="L25" s="13">
+        <v>1.75</v>
+      </c>
+      <c r="M25" s="4">
+        <v>0.73</v>
+      </c>
+      <c r="N25" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="O25" s="13">
+        <f t="shared" si="6"/>
+        <v>3.23</v>
+      </c>
+      <c r="P25" s="11">
         <f t="shared" si="8"/>
-        <v>4.5714285714285707E-2</v>
-      </c>
-      <c r="S24" s="18"/>
-      <c r="T24" s="7" t="s">
+        <v>0.64516129032258063</v>
+      </c>
+      <c r="Q25" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="R25" s="11">
+        <f t="shared" si="7"/>
+        <v>0.10483870967741937</v>
+      </c>
+      <c r="S25" s="20"/>
+    </row>
+    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A26" s="27">
+        <v>46090</v>
+      </c>
+      <c r="B26" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C26" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="D26" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="E26" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F26" s="24">
+        <v>1.7</v>
+      </c>
+      <c r="G26" s="31">
+        <v>3</v>
+      </c>
+      <c r="H26" s="31">
+        <v>0</v>
+      </c>
+      <c r="I26" s="24">
+        <v>1.91</v>
+      </c>
+      <c r="J26" s="24">
+        <v>1.22</v>
+      </c>
+      <c r="K26" s="24">
+        <v>1.38</v>
+      </c>
+      <c r="L26" s="24">
+        <v>1.76</v>
+      </c>
+      <c r="M26" s="16">
+        <v>0.79</v>
+      </c>
+      <c r="N26" s="25">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="O26" s="13">
+        <f t="shared" si="6"/>
+        <v>3.13</v>
+      </c>
+      <c r="P26" s="11">
+        <f t="shared" si="8"/>
+        <v>0.58823529411764708</v>
+      </c>
+      <c r="Q26" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="R26" s="11">
+        <f t="shared" si="7"/>
+        <v>8.1764705882352962E-2</v>
+      </c>
+      <c r="S26" s="18"/>
+    </row>
+    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A27" s="27">
+        <v>46090</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C27" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D27" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="E27" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F27" s="7">
+        <v>1.61</v>
+      </c>
+      <c r="G27" s="29">
+        <v>0</v>
+      </c>
+      <c r="H27" s="29">
+        <v>1</v>
+      </c>
+      <c r="I27" s="13">
+        <v>1.79</v>
+      </c>
+      <c r="J27" s="13">
+        <v>1.46</v>
+      </c>
+      <c r="K27" s="13">
+        <v>1.44</v>
+      </c>
+      <c r="L27" s="13">
+        <v>1.52</v>
+      </c>
+      <c r="M27" s="4">
+        <v>0.64</v>
+      </c>
+      <c r="N27" s="4">
+        <v>0.83</v>
+      </c>
+      <c r="O27" s="13">
+        <f t="shared" ref="O27:O30" si="9">I27+J27</f>
+        <v>3.25</v>
+      </c>
+      <c r="P27" s="11">
+        <f t="shared" si="8"/>
+        <v>0.6211180124223602</v>
+      </c>
+      <c r="Q27" s="4">
+        <v>0.73</v>
+      </c>
+      <c r="R27" s="11">
+        <f t="shared" si="7"/>
+        <v>0.10888198757763978</v>
+      </c>
+      <c r="S27" s="18"/>
+    </row>
+    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A28" s="27">
+        <v>46090</v>
+      </c>
+      <c r="B28" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="C28" s="7" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="25" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="S25" s="18"/>
-    </row>
-    <row r="26" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="S26" s="18"/>
-    </row>
-    <row r="27" spans="1:22" x14ac:dyDescent="0.25">
-      <c r="S27" s="18"/>
-    </row>
-    <row r="28" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="D28" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="E28" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F28" s="7">
+        <v>1.98</v>
+      </c>
+      <c r="G28" s="29">
+        <v>1</v>
+      </c>
+      <c r="H28" s="29">
+        <v>3</v>
+      </c>
+      <c r="I28" s="13">
+        <v>1.28</v>
+      </c>
+      <c r="J28" s="13">
+        <v>1.7</v>
+      </c>
+      <c r="K28" s="13">
+        <v>1.64</v>
+      </c>
+      <c r="L28" s="13">
+        <v>1.45</v>
+      </c>
+      <c r="M28" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="N28" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="O28" s="13">
+        <f t="shared" si="9"/>
+        <v>2.98</v>
+      </c>
+      <c r="P28" s="11">
+        <f t="shared" si="8"/>
+        <v>0.50505050505050508</v>
+      </c>
+      <c r="Q28" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="R28" s="11">
+        <f t="shared" si="7"/>
+        <v>0.16494949494949496</v>
+      </c>
       <c r="S28" s="18"/>
     </row>
     <row r="29" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A29" s="27">
+        <v>46090</v>
+      </c>
+      <c r="B29" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C29" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="D29" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F29" s="7">
+        <v>1.98</v>
+      </c>
+      <c r="G29" s="29">
+        <v>0</v>
+      </c>
+      <c r="H29" s="29">
+        <v>3</v>
+      </c>
+      <c r="I29" s="13">
+        <v>1.49</v>
+      </c>
+      <c r="J29" s="13">
+        <v>1.25</v>
+      </c>
+      <c r="K29" s="13">
+        <v>1.62</v>
+      </c>
+      <c r="L29" s="13">
+        <v>1.74</v>
+      </c>
+      <c r="M29" s="4">
+        <v>0.52</v>
+      </c>
+      <c r="N29" s="4">
+        <v>0.52</v>
+      </c>
+      <c r="O29" s="13">
+        <f t="shared" si="9"/>
+        <v>2.74</v>
+      </c>
+      <c r="P29" s="11">
+        <f t="shared" si="8"/>
+        <v>0.50505050505050508</v>
+      </c>
+      <c r="Q29" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="R29" s="11">
+        <f t="shared" si="7"/>
+        <v>9.4949494949494895E-2</v>
+      </c>
       <c r="S29" s="18"/>
     </row>
     <row r="30" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A30" s="27">
+        <v>46090</v>
+      </c>
+      <c r="B30" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="C30" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D30" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="F30" s="7">
+        <v>2.1</v>
+      </c>
+      <c r="G30" s="29">
+        <v>1</v>
+      </c>
+      <c r="H30" s="29">
+        <v>3</v>
+      </c>
+      <c r="I30" s="13">
+        <v>1.48</v>
+      </c>
+      <c r="J30" s="13">
+        <v>1.58</v>
+      </c>
+      <c r="K30" s="13">
+        <v>1.58</v>
+      </c>
+      <c r="L30" s="13">
+        <v>1.26</v>
+      </c>
+      <c r="M30" s="4">
+        <v>0.42</v>
+      </c>
+      <c r="N30" s="4">
+        <v>0.53</v>
+      </c>
+      <c r="O30" s="13">
+        <f t="shared" si="9"/>
+        <v>3.06</v>
+      </c>
+      <c r="P30" s="11">
+        <f t="shared" si="8"/>
+        <v>0.47619047619047616</v>
+      </c>
+      <c r="Q30" s="4">
+        <v>0.59</v>
+      </c>
+      <c r="R30" s="11">
+        <f t="shared" si="7"/>
+        <v>0.1138095238095238</v>
+      </c>
       <c r="S30" s="18"/>
     </row>
     <row r="31" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A31" s="27">
+        <v>46090</v>
+      </c>
+      <c r="B31" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C31" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D31" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="F31" s="3">
+        <v>1.94</v>
+      </c>
+      <c r="G31" s="32">
+        <v>1</v>
+      </c>
+      <c r="H31" s="32">
+        <v>1</v>
+      </c>
+      <c r="I31" s="3">
+        <v>1.43</v>
+      </c>
+      <c r="J31" s="3">
+        <v>1.1200000000000001</v>
+      </c>
+      <c r="K31" s="3">
+        <v>1.46</v>
+      </c>
+      <c r="L31" s="3">
+        <v>1.77</v>
+      </c>
+      <c r="M31" s="4">
+        <v>0.54</v>
+      </c>
+      <c r="N31" s="11">
+        <v>0.31</v>
+      </c>
+      <c r="O31" s="13">
+        <f t="shared" ref="O31:O66" si="10">I31+J31</f>
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="P31" s="11">
+        <f t="shared" ref="P31:P66" si="11">1/F31</f>
+        <v>0.51546391752577325</v>
+      </c>
+      <c r="Q31" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="R31" s="11">
+        <f t="shared" si="7"/>
+        <v>8.4536082474226726E-2</v>
+      </c>
       <c r="S31" s="18"/>
     </row>
     <row r="32" spans="1:22" x14ac:dyDescent="0.25">
+      <c r="A32" s="27">
+        <v>46091</v>
+      </c>
+      <c r="B32" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C32" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D32" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E32" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="F32" s="7">
+        <v>1.45</v>
+      </c>
+      <c r="G32" s="29">
+        <v>2</v>
+      </c>
+      <c r="H32" s="29">
+        <v>1</v>
+      </c>
+      <c r="I32" s="13">
+        <v>1.77</v>
+      </c>
+      <c r="J32" s="13">
+        <v>2.29</v>
+      </c>
+      <c r="K32" s="13">
+        <v>1.48</v>
+      </c>
+      <c r="L32" s="13">
+        <v>0.99</v>
+      </c>
+      <c r="M32" s="4">
+        <v>1</v>
+      </c>
+      <c r="N32" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="O32" s="13">
+        <f t="shared" si="10"/>
+        <v>4.0600000000000005</v>
+      </c>
+      <c r="P32" s="11">
+        <f t="shared" si="11"/>
+        <v>0.68965517241379315</v>
+      </c>
+      <c r="Q32" s="4">
+        <v>0.83</v>
+      </c>
+      <c r="R32" s="11">
+        <f t="shared" si="7"/>
+        <v>0.14034482758620681</v>
+      </c>
       <c r="S32" s="18"/>
     </row>
-    <row r="33" spans="19:19" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A33" s="27">
+        <v>46091</v>
+      </c>
+      <c r="B33" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C33" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D33" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="E33" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="F33" s="7">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="G33" s="29">
+        <v>2</v>
+      </c>
+      <c r="H33" s="29">
+        <v>1</v>
+      </c>
+      <c r="I33" s="13">
+        <v>1.77</v>
+      </c>
+      <c r="J33" s="13">
+        <v>2.29</v>
+      </c>
+      <c r="K33" s="13">
+        <v>1.48</v>
+      </c>
+      <c r="L33" s="13">
+        <v>0.99</v>
+      </c>
+      <c r="M33" s="4">
+        <v>1</v>
+      </c>
+      <c r="N33" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="O33" s="13">
+        <f t="shared" si="10"/>
+        <v>4.0600000000000005</v>
+      </c>
+      <c r="P33" s="11">
+        <f t="shared" si="11"/>
+        <v>0.48780487804878053</v>
+      </c>
+      <c r="Q33" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="R33" s="11">
+        <f t="shared" si="7"/>
+        <v>0.16219512195121949</v>
+      </c>
       <c r="S33" s="18"/>
     </row>
-    <row r="34" spans="19:19" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A34" s="27">
+        <v>46091</v>
+      </c>
+      <c r="B34" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C34" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="D34" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="E34" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="F34" s="7">
+        <v>1.48</v>
+      </c>
+      <c r="G34" s="29">
+        <v>2</v>
+      </c>
+      <c r="H34" s="29">
+        <v>1</v>
+      </c>
+      <c r="I34" s="13">
+        <v>1.83</v>
+      </c>
+      <c r="J34" s="13">
+        <v>2.0499999999999998</v>
+      </c>
+      <c r="K34" s="13">
+        <v>1.41</v>
+      </c>
+      <c r="L34" s="13">
+        <v>1.21</v>
+      </c>
+      <c r="M34" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="N34" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="O34" s="13">
+        <f t="shared" si="10"/>
+        <v>3.88</v>
+      </c>
+      <c r="P34" s="11">
+        <f t="shared" si="11"/>
+        <v>0.67567567567567566</v>
+      </c>
+      <c r="Q34" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="R34" s="11">
+        <f t="shared" si="7"/>
+        <v>0.12432432432432439</v>
+      </c>
       <c r="S34" s="18"/>
     </row>
-    <row r="35" spans="19:19" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A35" s="27">
+        <v>46091</v>
+      </c>
+      <c r="B35" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C35" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="D35" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="E35" s="3">
+        <v>2.5</v>
+      </c>
+      <c r="F35" s="7">
+        <v>1.48</v>
+      </c>
+      <c r="G35" s="29">
+        <v>1</v>
+      </c>
+      <c r="H35" s="29">
+        <v>6</v>
+      </c>
+      <c r="I35" s="13">
+        <v>1.7</v>
+      </c>
+      <c r="J35" s="13">
+        <v>2.12</v>
+      </c>
+      <c r="K35" s="13">
+        <v>1.33</v>
+      </c>
+      <c r="L35" s="13">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="M35" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="N35" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="O35" s="13">
+        <f t="shared" si="10"/>
+        <v>3.8200000000000003</v>
+      </c>
+      <c r="P35" s="11">
+        <f t="shared" si="11"/>
+        <v>0.67567567567567566</v>
+      </c>
+      <c r="Q35" s="4">
+        <v>0.79</v>
+      </c>
+      <c r="R35" s="11">
+        <f t="shared" si="7"/>
+        <v>0.11432432432432438</v>
+      </c>
       <c r="S35" s="18"/>
     </row>
-    <row r="36" spans="19:19" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A36" s="27">
+        <v>46091</v>
+      </c>
+      <c r="B36" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="C36" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="D36" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F36" s="7">
+        <v>1.83</v>
+      </c>
+      <c r="G36" s="29">
+        <v>1</v>
+      </c>
+      <c r="H36" s="29">
+        <v>3</v>
+      </c>
+      <c r="I36" s="13">
+        <v>1.55</v>
+      </c>
+      <c r="J36" s="13">
+        <v>1.4</v>
+      </c>
+      <c r="K36" s="13">
+        <v>1.41</v>
+      </c>
+      <c r="L36" s="13">
+        <v>1.21</v>
+      </c>
+      <c r="M36" s="4">
+        <v>0.71</v>
+      </c>
+      <c r="N36" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="O36" s="13">
+        <f t="shared" si="10"/>
+        <v>2.95</v>
+      </c>
+      <c r="P36" s="11">
+        <f t="shared" si="11"/>
+        <v>0.54644808743169393</v>
+      </c>
+      <c r="Q36" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="R36" s="11">
+        <f t="shared" si="7"/>
+        <v>0.10355191256830609</v>
+      </c>
       <c r="S36" s="18"/>
     </row>
-    <row r="37" spans="19:19" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A37" s="27">
+        <v>46091</v>
+      </c>
+      <c r="B37" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C37" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="D37" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="E37" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F37" s="7">
+        <v>1.75</v>
+      </c>
+      <c r="G37" s="29">
+        <v>5</v>
+      </c>
+      <c r="H37" s="29">
+        <v>2</v>
+      </c>
+      <c r="I37" s="13">
+        <v>1.55</v>
+      </c>
+      <c r="J37" s="13">
+        <v>1.55</v>
+      </c>
+      <c r="K37" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="L37" s="13">
+        <v>1.56</v>
+      </c>
+      <c r="M37" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="N37" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="O37" s="13">
+        <f t="shared" si="10"/>
+        <v>3.1</v>
+      </c>
+      <c r="P37" s="11">
+        <f t="shared" si="11"/>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="Q37" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="R37" s="11">
+        <f t="shared" si="7"/>
+        <v>7.8571428571428625E-2</v>
+      </c>
       <c r="S37" s="18"/>
     </row>
-    <row r="38" spans="19:19" x14ac:dyDescent="0.25">
-      <c r="S38" s="18"/>
+    <row r="38" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A38" s="27">
+        <v>46091</v>
+      </c>
+      <c r="B38" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D38" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="E38" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F38" s="7">
+        <v>1.7</v>
+      </c>
+      <c r="G38" s="29">
+        <v>1</v>
+      </c>
+      <c r="H38" s="29">
+        <v>2</v>
+      </c>
+      <c r="I38" s="7">
+        <v>1.31</v>
+      </c>
+      <c r="J38" s="7">
+        <v>1.28</v>
+      </c>
+      <c r="K38" s="13">
+        <v>1.51</v>
+      </c>
+      <c r="L38" s="13">
+        <v>1.69</v>
+      </c>
+      <c r="M38" s="4">
+        <v>0.78</v>
+      </c>
+      <c r="N38" s="4">
+        <v>0.59</v>
+      </c>
+      <c r="O38" s="13">
+        <f t="shared" si="10"/>
+        <v>2.59</v>
+      </c>
+      <c r="P38" s="11">
+        <f t="shared" si="11"/>
+        <v>0.58823529411764708</v>
+      </c>
+      <c r="Q38" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="R38" s="11">
+        <f t="shared" si="7"/>
+        <v>6.1764705882352944E-2</v>
+      </c>
+    </row>
+    <row r="39" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A39" s="27">
+        <v>46091</v>
+      </c>
+      <c r="B39" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C39" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="D39" s="7" t="s">
+        <v>119</v>
+      </c>
+      <c r="E39" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F39" s="7">
+        <v>2.35</v>
+      </c>
+      <c r="G39" s="29">
+        <v>1</v>
+      </c>
+      <c r="H39" s="29">
+        <v>1</v>
+      </c>
+      <c r="I39" s="13">
+        <v>1.7</v>
+      </c>
+      <c r="J39" s="13">
+        <v>1.24</v>
+      </c>
+      <c r="K39" s="13">
+        <v>1.04</v>
+      </c>
+      <c r="L39" s="13">
+        <v>1.31</v>
+      </c>
+      <c r="M39" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="N39" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="O39" s="13">
+        <f t="shared" si="10"/>
+        <v>2.94</v>
+      </c>
+      <c r="P39" s="11">
+        <f t="shared" si="11"/>
+        <v>0.42553191489361702</v>
+      </c>
+      <c r="Q39" s="4">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R39" s="11">
+        <f t="shared" si="7"/>
+        <v>0.15446808510638294</v>
+      </c>
+    </row>
+    <row r="40" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A40" s="27">
+        <v>46091</v>
+      </c>
+      <c r="B40" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C40" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="D40" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="E40" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F40" s="7">
+        <v>2.1</v>
+      </c>
+      <c r="G40" s="29">
+        <v>4</v>
+      </c>
+      <c r="H40" s="29">
+        <v>4</v>
+      </c>
+      <c r="I40" s="13">
+        <v>1.77</v>
+      </c>
+      <c r="J40" s="13">
+        <v>1.49</v>
+      </c>
+      <c r="K40" s="13">
+        <v>0.87</v>
+      </c>
+      <c r="L40" s="13">
+        <v>1.33</v>
+      </c>
+      <c r="M40" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="N40" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="O40" s="13">
+        <f t="shared" si="10"/>
+        <v>3.26</v>
+      </c>
+      <c r="P40" s="11">
+        <f t="shared" si="11"/>
+        <v>0.47619047619047616</v>
+      </c>
+      <c r="Q40" s="4">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="R40" s="11">
+        <f t="shared" si="7"/>
+        <v>9.3809523809523787E-2</v>
+      </c>
+    </row>
+    <row r="41" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A41" s="27">
+        <v>46092</v>
+      </c>
+      <c r="B41" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="C41" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="D41" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="E41" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="F41" s="7">
+        <v>1.65</v>
+      </c>
+      <c r="G41" s="29">
+        <v>3</v>
+      </c>
+      <c r="H41" s="29">
+        <v>0</v>
+      </c>
+      <c r="I41" s="13">
+        <v>1.61</v>
+      </c>
+      <c r="J41" s="13">
+        <v>1.8</v>
+      </c>
+      <c r="K41" s="13">
+        <v>1.91</v>
+      </c>
+      <c r="L41" s="13">
+        <v>0.93</v>
+      </c>
+      <c r="M41" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="N41" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="O41" s="13">
+        <f t="shared" si="10"/>
+        <v>3.41</v>
+      </c>
+      <c r="P41" s="11">
+        <f t="shared" si="11"/>
+        <v>0.60606060606060608</v>
+      </c>
+      <c r="Q41" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="R41" s="11">
+        <f t="shared" si="7"/>
+        <v>0.14393939393939392</v>
+      </c>
+    </row>
+    <row r="42" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A42" s="27">
+        <v>46093</v>
+      </c>
+      <c r="B42" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C42" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D42" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="E42" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F42" s="7">
+        <v>1.72</v>
+      </c>
+      <c r="G42" s="29">
+        <v>1</v>
+      </c>
+      <c r="H42" s="29">
+        <v>3</v>
+      </c>
+      <c r="I42" s="13">
+        <v>1.37</v>
+      </c>
+      <c r="J42" s="13">
+        <v>1.31</v>
+      </c>
+      <c r="K42" s="13">
+        <v>1.65</v>
+      </c>
+      <c r="L42" s="13">
+        <v>1.56</v>
+      </c>
+      <c r="M42" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="N42" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="O42" s="13">
+        <f t="shared" si="10"/>
+        <v>2.68</v>
+      </c>
+      <c r="P42" s="11">
+        <f t="shared" si="11"/>
+        <v>0.58139534883720934</v>
+      </c>
+      <c r="Q42" s="4">
+        <v>0.69</v>
+      </c>
+      <c r="R42" s="11">
+        <f t="shared" si="7"/>
+        <v>0.10860465116279061</v>
+      </c>
+    </row>
+    <row r="43" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A43" s="27">
+        <v>46093</v>
+      </c>
+      <c r="B43" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C43" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="D43" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="E43" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F43" s="7">
+        <v>1.76</v>
+      </c>
+      <c r="G43" s="29">
+        <v>0</v>
+      </c>
+      <c r="H43" s="29">
+        <v>0</v>
+      </c>
+      <c r="I43" s="13">
+        <v>1.51</v>
+      </c>
+      <c r="J43" s="13">
+        <v>1.23</v>
+      </c>
+      <c r="K43" s="13">
+        <v>1.21</v>
+      </c>
+      <c r="L43" s="13">
+        <v>1.86</v>
+      </c>
+      <c r="M43" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="N43" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="O43" s="13">
+        <f t="shared" si="10"/>
+        <v>2.74</v>
+      </c>
+      <c r="P43" s="11">
+        <f t="shared" si="11"/>
+        <v>0.56818181818181823</v>
+      </c>
+      <c r="Q43" s="4">
+        <v>0.66</v>
+      </c>
+      <c r="R43" s="11">
+        <f t="shared" si="7"/>
+        <v>9.1818181818181799E-2</v>
+      </c>
+    </row>
+    <row r="44" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A44" s="27">
+        <v>46093</v>
+      </c>
+      <c r="B44" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="C44" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="D44" s="7" t="s">
+        <v>133</v>
+      </c>
+      <c r="E44" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F44" s="7">
+        <v>1.76</v>
+      </c>
+      <c r="G44" s="29">
+        <v>1</v>
+      </c>
+      <c r="H44" s="29">
+        <v>1</v>
+      </c>
+      <c r="I44" s="13">
+        <v>1.35</v>
+      </c>
+      <c r="J44" s="13">
+        <v>1.31</v>
+      </c>
+      <c r="K44" s="13">
+        <v>1.05</v>
+      </c>
+      <c r="L44" s="13">
+        <v>1.39</v>
+      </c>
+      <c r="M44" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="N44" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="O44" s="13">
+        <f t="shared" si="10"/>
+        <v>2.66</v>
+      </c>
+      <c r="P44" s="11">
+        <f t="shared" si="11"/>
+        <v>0.56818181818181823</v>
+      </c>
+      <c r="Q44" s="4">
+        <v>0.66</v>
+      </c>
+      <c r="R44" s="11">
+        <f t="shared" si="7"/>
+        <v>9.1818181818181799E-2</v>
+      </c>
+    </row>
+    <row r="45" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A45" s="27">
+        <v>46093</v>
+      </c>
+      <c r="B45" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C45" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="D45" s="7" t="s">
+        <v>132</v>
+      </c>
+      <c r="E45" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F45" s="7">
+        <v>1.72</v>
+      </c>
+      <c r="G45" s="29">
+        <v>1</v>
+      </c>
+      <c r="H45" s="29">
+        <v>2</v>
+      </c>
+      <c r="I45" s="13">
+        <v>1.6</v>
+      </c>
+      <c r="J45" s="13">
+        <v>1.37</v>
+      </c>
+      <c r="K45" s="13">
+        <v>1.65</v>
+      </c>
+      <c r="L45" s="13">
+        <v>1.6</v>
+      </c>
+      <c r="M45" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="N45" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="O45" s="13">
+        <f t="shared" si="10"/>
+        <v>2.97</v>
+      </c>
+      <c r="P45" s="11">
+        <f t="shared" si="11"/>
+        <v>0.58139534883720934</v>
+      </c>
+      <c r="Q45" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="R45" s="11">
+        <f t="shared" si="7"/>
+        <v>8.8604651162790704E-2</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A46" s="27">
+        <v>46093</v>
+      </c>
+      <c r="B46" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>134</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E46" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="F46" s="7">
+        <v>1.9</v>
+      </c>
+      <c r="G46" s="29">
+        <v>2</v>
+      </c>
+      <c r="H46" s="29">
+        <v>2</v>
+      </c>
+      <c r="I46" s="13">
+        <v>1.49</v>
+      </c>
+      <c r="J46" s="13">
+        <v>1.36</v>
+      </c>
+      <c r="K46" s="13">
+        <v>1.23</v>
+      </c>
+      <c r="L46" s="13">
+        <v>1.67</v>
+      </c>
+      <c r="M46" s="4">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="N46" s="4">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="O46" s="13">
+        <f t="shared" si="10"/>
+        <v>2.85</v>
+      </c>
+      <c r="P46" s="11">
+        <f t="shared" si="11"/>
+        <v>0.52631578947368418</v>
+      </c>
+      <c r="Q46" s="4">
+        <v>0.61</v>
+      </c>
+      <c r="R46" s="11">
+        <f t="shared" si="7"/>
+        <v>8.3684210526315805E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A47" s="27">
+        <v>46093</v>
+      </c>
+      <c r="B47" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C47" s="7" t="s">
+        <v>137</v>
+      </c>
+      <c r="D47" s="7" t="s">
+        <v>138</v>
+      </c>
+      <c r="E47" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F47" s="7">
+        <v>1.67</v>
+      </c>
+      <c r="G47" s="29">
+        <v>1</v>
+      </c>
+      <c r="H47" s="29">
+        <v>3</v>
+      </c>
+      <c r="I47" s="13">
+        <v>2.17</v>
+      </c>
+      <c r="J47" s="13">
+        <v>1.97</v>
+      </c>
+      <c r="K47" s="13">
+        <v>1.37</v>
+      </c>
+      <c r="L47" s="13">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="M47" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="N47" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="O47" s="13">
+        <f t="shared" si="10"/>
+        <v>4.1399999999999997</v>
+      </c>
+      <c r="P47" s="11">
+        <f t="shared" si="11"/>
+        <v>0.5988023952095809</v>
+      </c>
+      <c r="Q47" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="R47" s="11">
+        <f t="shared" si="7"/>
+        <v>5.1197604790419127E-2</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" x14ac:dyDescent="0.25">
+      <c r="A48" s="27">
+        <v>46093</v>
+      </c>
+      <c r="B48" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C48" s="7" t="s">
+        <v>142</v>
+      </c>
+      <c r="D48" s="7" t="s">
+        <v>141</v>
+      </c>
+      <c r="E48" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F48" s="7">
+        <v>2.35</v>
+      </c>
+      <c r="G48" s="29">
+        <v>1</v>
+      </c>
+      <c r="H48" s="29">
+        <v>1</v>
+      </c>
+      <c r="I48" s="13">
+        <v>1.31</v>
+      </c>
+      <c r="J48" s="13">
+        <v>1.57</v>
+      </c>
+      <c r="K48" s="13">
+        <v>0.8</v>
+      </c>
+      <c r="L48" s="13">
+        <v>1.33</v>
+      </c>
+      <c r="M48" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="N48" s="4">
+        <v>0.2</v>
+      </c>
+      <c r="O48" s="13">
+        <f t="shared" si="10"/>
+        <v>2.88</v>
+      </c>
+      <c r="P48" s="11">
+        <f t="shared" si="11"/>
+        <v>0.42553191489361702</v>
+      </c>
+      <c r="Q48" s="4">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="R48" s="11">
+        <f t="shared" si="7"/>
+        <v>0.12446808510638302</v>
+      </c>
+    </row>
+    <row r="49" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A49" s="27">
+        <v>46093</v>
+      </c>
+      <c r="B49" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C49" s="7" t="s">
+        <v>143</v>
+      </c>
+      <c r="D49" s="7" t="s">
+        <v>140</v>
+      </c>
+      <c r="E49" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F49" s="7">
+        <v>1.75</v>
+      </c>
+      <c r="G49" s="29">
+        <v>0</v>
+      </c>
+      <c r="H49" s="29">
+        <v>2</v>
+      </c>
+      <c r="I49" s="13">
+        <v>1.54</v>
+      </c>
+      <c r="J49" s="13">
+        <v>1.74</v>
+      </c>
+      <c r="K49" s="13">
+        <v>1.4</v>
+      </c>
+      <c r="L49" s="13">
+        <v>1.74</v>
+      </c>
+      <c r="M49" s="4">
+        <v>1</v>
+      </c>
+      <c r="N49" s="4">
+        <v>1</v>
+      </c>
+      <c r="O49" s="13">
+        <f t="shared" si="10"/>
+        <v>3.2800000000000002</v>
+      </c>
+      <c r="P49" s="11">
+        <f t="shared" si="11"/>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="Q49" s="4">
+        <v>0.69</v>
+      </c>
+      <c r="R49" s="11">
+        <f t="shared" si="7"/>
+        <v>0.11857142857142855</v>
+      </c>
+    </row>
+    <row r="50" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A50" s="27">
+        <v>46094</v>
+      </c>
+      <c r="B50" s="7" t="s">
+        <v>144</v>
+      </c>
+      <c r="C50" s="7" t="s">
+        <v>145</v>
+      </c>
+      <c r="D50" s="7" t="s">
+        <v>148</v>
+      </c>
+      <c r="E50" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F50" s="7">
+        <v>1.53</v>
+      </c>
+      <c r="G50" s="29">
+        <v>2</v>
+      </c>
+      <c r="H50" s="29">
+        <v>0</v>
+      </c>
+      <c r="I50" s="13">
+        <v>1.48</v>
+      </c>
+      <c r="J50" s="13">
+        <v>1.1399999999999999</v>
+      </c>
+      <c r="K50" s="13">
+        <v>1.79</v>
+      </c>
+      <c r="L50" s="13">
+        <v>1.97</v>
+      </c>
+      <c r="M50" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="N50" s="4">
+        <v>0.62</v>
+      </c>
+      <c r="O50" s="13">
+        <f t="shared" si="10"/>
+        <v>2.62</v>
+      </c>
+      <c r="P50" s="11">
+        <f t="shared" si="11"/>
+        <v>0.65359477124183007</v>
+      </c>
+      <c r="Q50" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="R50" s="11">
+        <f t="shared" si="7"/>
+        <v>4.6405228758169881E-2</v>
+      </c>
+    </row>
+    <row r="51" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A51" s="27">
+        <v>46094</v>
+      </c>
+      <c r="B51" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C51" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D51" s="7" t="s">
+        <v>146</v>
+      </c>
+      <c r="E51" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F51" s="7">
+        <v>1.65</v>
+      </c>
+      <c r="G51" s="29">
+        <v>2</v>
+      </c>
+      <c r="H51" s="29">
+        <v>0</v>
+      </c>
+      <c r="I51" s="13">
+        <v>1.61</v>
+      </c>
+      <c r="J51" s="13">
+        <v>1.25</v>
+      </c>
+      <c r="K51" s="13">
+        <v>1.31</v>
+      </c>
+      <c r="L51" s="13">
+        <v>1.55</v>
+      </c>
+      <c r="M51" s="4">
+        <v>0.79</v>
+      </c>
+      <c r="N51" s="4">
+        <v>0.44</v>
+      </c>
+      <c r="O51" s="13">
+        <f t="shared" si="10"/>
+        <v>2.8600000000000003</v>
+      </c>
+      <c r="P51" s="11">
+        <f t="shared" si="11"/>
+        <v>0.60606060606060608</v>
+      </c>
+      <c r="Q51" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="R51" s="11">
+        <f t="shared" si="7"/>
+        <v>7.3939393939393971E-2</v>
+      </c>
+    </row>
+    <row r="52" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A52" s="27">
+        <v>46095</v>
+      </c>
+      <c r="B52" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="C52" s="7" t="s">
+        <v>154</v>
+      </c>
+      <c r="D52" s="7" t="s">
+        <v>155</v>
+      </c>
+      <c r="E52" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F52" s="7">
+        <v>1.8</v>
+      </c>
+      <c r="G52" s="29">
+        <v>1</v>
+      </c>
+      <c r="H52" s="29">
+        <v>2</v>
+      </c>
+      <c r="I52" s="13">
+        <v>1.94</v>
+      </c>
+      <c r="J52" s="13">
+        <v>1.48</v>
+      </c>
+      <c r="K52" s="13">
+        <v>1.5</v>
+      </c>
+      <c r="L52" s="13">
+        <v>1.58</v>
+      </c>
+      <c r="M52" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="N52" s="4">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="O52" s="13">
+        <f t="shared" si="10"/>
+        <v>3.42</v>
+      </c>
+      <c r="P52" s="11">
+        <f t="shared" si="11"/>
+        <v>0.55555555555555558</v>
+      </c>
+      <c r="Q52" s="4">
+        <v>0.7</v>
+      </c>
+      <c r="R52" s="11">
+        <f t="shared" si="7"/>
+        <v>0.14444444444444438</v>
+      </c>
+    </row>
+    <row r="53" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A53" s="27">
+        <v>46095</v>
+      </c>
+      <c r="B53" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="D53" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F53" s="7">
+        <v>1.7</v>
+      </c>
+      <c r="G53" s="29">
+        <v>1</v>
+      </c>
+      <c r="H53" s="29">
+        <v>2</v>
+      </c>
+      <c r="I53" s="13">
+        <v>1.46</v>
+      </c>
+      <c r="J53" s="13">
+        <v>1.7</v>
+      </c>
+      <c r="K53" s="13">
+        <v>1.56</v>
+      </c>
+      <c r="L53" s="13">
+        <v>1.34</v>
+      </c>
+      <c r="M53" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="N53" s="4">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="O53" s="13">
+        <f t="shared" si="10"/>
+        <v>3.16</v>
+      </c>
+      <c r="P53" s="11">
+        <f t="shared" si="11"/>
+        <v>0.58823529411764708</v>
+      </c>
+      <c r="Q53" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="R53" s="11">
+        <f t="shared" si="7"/>
+        <v>8.1764705882352962E-2</v>
+      </c>
+    </row>
+    <row r="54" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A54" s="27">
+        <v>46095</v>
+      </c>
+      <c r="B54" s="7" t="s">
+        <v>149</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="D54" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="E54" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F54" s="7">
+        <v>1.65</v>
+      </c>
+      <c r="G54" s="29">
+        <v>2</v>
+      </c>
+      <c r="H54" s="29">
+        <v>0</v>
+      </c>
+      <c r="I54" s="13">
+        <v>1.27</v>
+      </c>
+      <c r="J54" s="13">
+        <v>1.51</v>
+      </c>
+      <c r="K54" s="13">
+        <v>1.37</v>
+      </c>
+      <c r="L54" s="13">
+        <v>1.54</v>
+      </c>
+      <c r="M54" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="N54" s="4">
+        <v>0.71</v>
+      </c>
+      <c r="O54" s="13">
+        <f t="shared" si="10"/>
+        <v>2.7800000000000002</v>
+      </c>
+      <c r="P54" s="11">
+        <f t="shared" si="11"/>
+        <v>0.60606060606060608</v>
+      </c>
+      <c r="Q54" s="4">
+        <v>0.68</v>
+      </c>
+      <c r="R54" s="11">
+        <f t="shared" si="7"/>
+        <v>7.3939393939393971E-2</v>
+      </c>
+    </row>
+    <row r="55" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A55" s="27">
+        <v>46095</v>
+      </c>
+      <c r="B55" s="7" t="s">
+        <v>28</v>
+      </c>
+      <c r="C55" s="7" t="s">
+        <v>150</v>
+      </c>
+      <c r="D55" s="7" t="s">
+        <v>151</v>
+      </c>
+      <c r="E55" s="7">
+        <v>2.5</v>
+      </c>
+      <c r="F55" s="7">
+        <v>1.77</v>
+      </c>
+      <c r="G55" s="29">
+        <v>2</v>
+      </c>
+      <c r="H55" s="29">
+        <v>1</v>
+      </c>
+      <c r="I55" s="13">
+        <v>1.66</v>
+      </c>
+      <c r="J55" s="13">
+        <v>1.43</v>
+      </c>
+      <c r="K55" s="13">
+        <v>1.4</v>
+      </c>
+      <c r="L55" s="13">
+        <v>1.96</v>
+      </c>
+      <c r="M55" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="N55" s="4">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="O55" s="13">
+        <f t="shared" si="10"/>
+        <v>3.09</v>
+      </c>
+      <c r="P55" s="11">
+        <f t="shared" si="11"/>
+        <v>0.56497175141242939</v>
+      </c>
+      <c r="Q55" s="4">
+        <v>0.66</v>
+      </c>
+      <c r="R55" s="11">
+        <f t="shared" si="7"/>
+        <v>9.5028248587570641E-2</v>
+      </c>
+    </row>
+    <row r="56" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A56" s="27">
+        <v>46095</v>
+      </c>
+      <c r="B56" s="7" t="s">
+        <v>156</v>
+      </c>
+      <c r="C56" s="7" t="s">
+        <v>159</v>
+      </c>
+      <c r="D56" s="7" t="s">
+        <v>160</v>
+      </c>
+      <c r="E56" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F56" s="7">
+        <v>1.75</v>
+      </c>
+      <c r="G56" s="29">
+        <v>0</v>
+      </c>
+      <c r="H56" s="29">
+        <v>2</v>
+      </c>
+      <c r="I56" s="13">
+        <v>0.86</v>
+      </c>
+      <c r="J56" s="13">
+        <v>1.25</v>
+      </c>
+      <c r="K56" s="13">
+        <v>1.96</v>
+      </c>
+      <c r="L56" s="13">
+        <v>1.32</v>
+      </c>
+      <c r="M56" s="4">
+        <v>1</v>
+      </c>
+      <c r="N56" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="O56" s="13">
+        <f t="shared" si="10"/>
+        <v>2.11</v>
+      </c>
+      <c r="P56" s="11">
+        <f t="shared" si="11"/>
+        <v>0.5714285714285714</v>
+      </c>
+      <c r="Q56" s="4">
+        <v>0.62</v>
+      </c>
+      <c r="R56" s="11">
+        <f t="shared" si="7"/>
+        <v>4.8571428571428599E-2</v>
+      </c>
+    </row>
+    <row r="57" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A57" s="27">
+        <v>46095</v>
+      </c>
+      <c r="B57" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C57" s="7" t="s">
+        <v>157</v>
+      </c>
+      <c r="D57" s="7" t="s">
+        <v>158</v>
+      </c>
+      <c r="E57" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F57" s="7">
+        <v>1.95</v>
+      </c>
+      <c r="G57" s="29">
+        <v>2</v>
+      </c>
+      <c r="H57" s="29">
+        <v>0</v>
+      </c>
+      <c r="I57" s="13">
+        <v>1.77</v>
+      </c>
+      <c r="J57" s="13">
+        <v>1.3</v>
+      </c>
+      <c r="K57" s="13">
+        <v>0.97</v>
+      </c>
+      <c r="L57" s="13">
+        <v>1.42</v>
+      </c>
+      <c r="M57" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="N57" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="O57" s="13">
+        <f t="shared" si="10"/>
+        <v>3.0700000000000003</v>
+      </c>
+      <c r="P57" s="11">
+        <f t="shared" si="11"/>
+        <v>0.51282051282051289</v>
+      </c>
+      <c r="Q57" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="R57" s="11">
+        <f t="shared" si="7"/>
+        <v>8.7179487179487092E-2</v>
+      </c>
+    </row>
+    <row r="58" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A58" s="27">
+        <v>46096</v>
+      </c>
+      <c r="B58" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="C58" s="7" t="s">
+        <v>161</v>
+      </c>
+      <c r="D58" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="E58" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F58" s="7">
+        <v>1.57</v>
+      </c>
+      <c r="G58" s="29">
+        <v>1</v>
+      </c>
+      <c r="H58" s="29">
+        <v>1</v>
+      </c>
+      <c r="I58" s="13">
+        <v>1.66</v>
+      </c>
+      <c r="J58" s="13">
+        <v>1.17</v>
+      </c>
+      <c r="K58" s="13">
+        <v>1.39</v>
+      </c>
+      <c r="L58" s="13">
+        <v>1.44</v>
+      </c>
+      <c r="M58" s="4">
+        <v>0.54</v>
+      </c>
+      <c r="N58" s="4">
+        <v>0.62</v>
+      </c>
+      <c r="O58" s="13">
+        <f t="shared" si="10"/>
+        <v>2.83</v>
+      </c>
+      <c r="P58" s="11">
+        <f t="shared" si="11"/>
+        <v>0.63694267515923564</v>
+      </c>
+      <c r="Q58" s="4">
+        <v>0.73</v>
+      </c>
+      <c r="R58" s="11">
+        <f t="shared" si="7"/>
+        <v>9.3057324840764344E-2</v>
+      </c>
+    </row>
+    <row r="59" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A59" s="27">
+        <v>46096</v>
+      </c>
+      <c r="B59" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C59" s="7" t="s">
+        <v>162</v>
+      </c>
+      <c r="D59" s="7" t="s">
+        <v>163</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F59" s="7">
+        <v>1.9</v>
+      </c>
+      <c r="G59" s="29">
+        <v>2</v>
+      </c>
+      <c r="H59" s="29">
+        <v>1</v>
+      </c>
+      <c r="I59" s="13">
+        <v>1.55</v>
+      </c>
+      <c r="J59" s="13">
+        <v>1.53</v>
+      </c>
+      <c r="K59" s="13">
+        <v>0.71</v>
+      </c>
+      <c r="L59" s="13">
+        <v>1.67</v>
+      </c>
+      <c r="M59" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="N59" s="4">
+        <v>0.8</v>
+      </c>
+      <c r="O59" s="13">
+        <f t="shared" si="10"/>
+        <v>3.08</v>
+      </c>
+      <c r="P59" s="11">
+        <f t="shared" si="11"/>
+        <v>0.52631578947368418</v>
+      </c>
+      <c r="Q59" s="4">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="R59" s="11">
+        <f t="shared" si="7"/>
+        <v>5.3684210526315779E-2</v>
+      </c>
+    </row>
+    <row r="60" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A60" s="27">
+        <v>46096</v>
+      </c>
+      <c r="B60" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C60" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="D60" s="7" t="s">
+        <v>165</v>
+      </c>
+      <c r="E60" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F60" s="7">
+        <v>1.95</v>
+      </c>
+      <c r="G60" s="29">
+        <v>2</v>
+      </c>
+      <c r="H60" s="29">
+        <v>2</v>
+      </c>
+      <c r="I60" s="13">
+        <v>1.35</v>
+      </c>
+      <c r="J60" s="13">
+        <v>1.26</v>
+      </c>
+      <c r="K60" s="13">
+        <v>1.35</v>
+      </c>
+      <c r="L60" s="13">
+        <v>1.21</v>
+      </c>
+      <c r="M60" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="N60" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="O60" s="13">
+        <f t="shared" si="10"/>
+        <v>2.6100000000000003</v>
+      </c>
+      <c r="P60" s="11">
+        <f t="shared" si="11"/>
+        <v>0.51282051282051289</v>
+      </c>
+      <c r="Q60" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="R60" s="11">
+        <f t="shared" si="7"/>
+        <v>8.7179487179487092E-2</v>
+      </c>
+    </row>
+    <row r="61" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A61" s="27">
+        <v>46096</v>
+      </c>
+      <c r="B61" s="7" t="s">
+        <v>166</v>
+      </c>
+      <c r="C61" s="7" t="s">
+        <v>167</v>
+      </c>
+      <c r="D61" s="7" t="s">
+        <v>168</v>
+      </c>
+      <c r="E61" s="7" t="s">
+        <v>147</v>
+      </c>
+      <c r="F61" s="7">
+        <v>1.65</v>
+      </c>
+      <c r="G61" s="29">
+        <v>1</v>
+      </c>
+      <c r="H61" s="29">
+        <v>2</v>
+      </c>
+      <c r="I61" s="13">
+        <v>1.8</v>
+      </c>
+      <c r="J61" s="13">
+        <v>1.58</v>
+      </c>
+      <c r="K61" s="13">
+        <v>1.4</v>
+      </c>
+      <c r="L61" s="13">
+        <v>1.19</v>
+      </c>
+      <c r="M61" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="N61" s="4">
+        <v>0.25</v>
+      </c>
+      <c r="O61" s="13">
+        <f t="shared" si="10"/>
+        <v>3.38</v>
+      </c>
+      <c r="P61" s="11">
+        <f t="shared" si="11"/>
+        <v>0.60606060606060608</v>
+      </c>
+      <c r="Q61" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="R61" s="11">
+        <f t="shared" si="7"/>
+        <v>0.14393939393939392</v>
+      </c>
+    </row>
+    <row r="62" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A62" s="27">
+        <v>46097</v>
+      </c>
+      <c r="B62" s="7" t="s">
+        <v>169</v>
+      </c>
+      <c r="C62" s="7" t="s">
+        <v>176</v>
+      </c>
+      <c r="D62" s="7" t="s">
+        <v>175</v>
+      </c>
+      <c r="E62" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F62" s="7">
+        <v>1.77</v>
+      </c>
+      <c r="G62" s="29">
+        <v>2</v>
+      </c>
+      <c r="H62" s="29">
+        <v>2</v>
+      </c>
+      <c r="I62" s="13">
+        <v>1.47</v>
+      </c>
+      <c r="J62" s="13">
+        <v>1.49</v>
+      </c>
+      <c r="K62" s="13">
+        <v>1.84</v>
+      </c>
+      <c r="L62" s="13">
+        <v>1.74</v>
+      </c>
+      <c r="M62" s="4">
+        <v>0.77</v>
+      </c>
+      <c r="N62" s="4">
+        <v>0.62</v>
+      </c>
+      <c r="O62" s="13">
+        <f t="shared" si="10"/>
+        <v>2.96</v>
+      </c>
+      <c r="P62" s="11">
+        <f t="shared" si="11"/>
+        <v>0.56497175141242939</v>
+      </c>
+      <c r="Q62" s="4">
+        <v>0.65</v>
+      </c>
+      <c r="R62" s="11">
+        <f t="shared" si="7"/>
+        <v>8.5028248587570632E-2</v>
+      </c>
+    </row>
+    <row r="63" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A63" s="27">
+        <v>46097</v>
+      </c>
+      <c r="B63" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C63" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D63" s="7" t="s">
+        <v>174</v>
+      </c>
+      <c r="E63" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F63" s="7">
+        <v>2.25</v>
+      </c>
+      <c r="G63" s="29">
+        <v>2</v>
+      </c>
+      <c r="H63" s="29">
+        <v>1</v>
+      </c>
+      <c r="I63" s="13">
+        <v>1.39</v>
+      </c>
+      <c r="J63" s="13">
+        <v>1.1599999999999999</v>
+      </c>
+      <c r="K63" s="13">
+        <v>1.73</v>
+      </c>
+      <c r="L63" s="13">
+        <v>1.41</v>
+      </c>
+      <c r="M63" s="4">
+        <v>0.5</v>
+      </c>
+      <c r="N63" s="4">
+        <v>1</v>
+      </c>
+      <c r="O63" s="13">
+        <f t="shared" si="10"/>
+        <v>2.5499999999999998</v>
+      </c>
+      <c r="P63" s="11">
+        <f t="shared" si="11"/>
+        <v>0.44444444444444442</v>
+      </c>
+      <c r="Q63" s="4">
+        <v>0.52</v>
+      </c>
+      <c r="R63" s="11">
+        <f t="shared" si="7"/>
+        <v>7.5555555555555598E-2</v>
+      </c>
+    </row>
+    <row r="64" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A64" s="27">
+        <v>46097</v>
+      </c>
+      <c r="B64" s="7" t="s">
+        <v>170</v>
+      </c>
+      <c r="C64" s="7" t="s">
+        <v>171</v>
+      </c>
+      <c r="D64" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E64" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F64" s="7">
+        <v>1.85</v>
+      </c>
+      <c r="G64" s="29">
+        <v>2</v>
+      </c>
+      <c r="H64" s="29">
+        <v>1</v>
+      </c>
+      <c r="I64" s="13">
+        <v>1.91</v>
+      </c>
+      <c r="J64" s="13">
+        <v>1.51</v>
+      </c>
+      <c r="K64" s="13">
+        <v>1.29</v>
+      </c>
+      <c r="L64" s="13">
+        <v>1.61</v>
+      </c>
+      <c r="M64" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="N64" s="4">
+        <v>0.53</v>
+      </c>
+      <c r="O64" s="13">
+        <f t="shared" si="10"/>
+        <v>3.42</v>
+      </c>
+      <c r="P64" s="11">
+        <f t="shared" si="11"/>
+        <v>0.54054054054054046</v>
+      </c>
+      <c r="Q64" s="4">
+        <v>0.61</v>
+      </c>
+      <c r="R64" s="11">
+        <f t="shared" si="7"/>
+        <v>6.9459459459459527E-2</v>
+      </c>
+    </row>
+    <row r="65" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A65" s="27">
+        <v>46097</v>
+      </c>
+      <c r="B65" s="7" t="s">
+        <v>139</v>
+      </c>
+      <c r="C65" s="7" t="s">
+        <v>178</v>
+      </c>
+      <c r="D65" s="7" t="s">
+        <v>177</v>
+      </c>
+      <c r="E65" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F65" s="7">
+        <v>1.77</v>
+      </c>
+      <c r="G65" s="29">
+        <v>1</v>
+      </c>
+      <c r="H65" s="29">
+        <v>1</v>
+      </c>
+      <c r="I65" s="13">
+        <v>1.74</v>
+      </c>
+      <c r="J65" s="13">
+        <v>0.83</v>
+      </c>
+      <c r="K65" s="13">
+        <v>1.6</v>
+      </c>
+      <c r="L65" s="13">
+        <v>1.62</v>
+      </c>
+      <c r="M65" s="4">
+        <v>0.4</v>
+      </c>
+      <c r="N65" s="4">
+        <v>0.67</v>
+      </c>
+      <c r="O65" s="13">
+        <f t="shared" si="10"/>
+        <v>2.57</v>
+      </c>
+      <c r="P65" s="11">
+        <f t="shared" si="11"/>
+        <v>0.56497175141242939</v>
+      </c>
+      <c r="Q65" s="4">
+        <v>0.63</v>
+      </c>
+      <c r="R65" s="11">
+        <f t="shared" si="7"/>
+        <v>6.5028248587570614E-2</v>
+      </c>
+    </row>
+    <row r="66" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="A66" s="27">
+        <v>46097</v>
+      </c>
+      <c r="B66" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C66" s="7" t="s">
+        <v>179</v>
+      </c>
+      <c r="D66" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E66" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="F66" s="7">
+        <v>2.1</v>
+      </c>
+      <c r="G66" s="29">
+        <v>2</v>
+      </c>
+      <c r="H66" s="29">
+        <v>1</v>
+      </c>
+      <c r="I66" s="13">
+        <v>1.33</v>
+      </c>
+      <c r="J66" s="13">
+        <v>1.34</v>
+      </c>
+      <c r="K66" s="13">
+        <v>1.02</v>
+      </c>
+      <c r="L66" s="13">
+        <v>1.33</v>
+      </c>
+      <c r="M66" s="4">
+        <v>0.6</v>
+      </c>
+      <c r="N66" s="4">
+        <v>0.75</v>
+      </c>
+      <c r="O66" s="13">
+        <f t="shared" si="10"/>
+        <v>2.67</v>
+      </c>
+      <c r="P66" s="11">
+        <f t="shared" si="11"/>
+        <v>0.47619047619047616</v>
+      </c>
+      <c r="Q66" s="4">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="R66" s="11">
+        <f t="shared" si="7"/>
+        <v>7.380952380952388E-2</v>
+      </c>
     </row>
   </sheetData>
-  <conditionalFormatting sqref="S1 S18:S1048576">
-    <cfRule type="containsText" dxfId="35" priority="11" operator="containsText" text="SUPER BTTS">
+  <conditionalFormatting sqref="S1 S18:S24 S26:S1048576">
+    <cfRule type="containsText" dxfId="8" priority="11" operator="containsText" text="SUPER BTTS">
       <formula>NOT(ISERROR(SEARCH("SUPER BTTS",S1)))</formula>
     </cfRule>
     <cfRule type="cellIs" priority="14" operator="between">
@@ -2831,35 +5100,35 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="U1:U1048576">
-    <cfRule type="containsText" dxfId="34" priority="12" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="7" priority="12" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",U1)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="33" priority="13" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="6" priority="13" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",U1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V7:V9">
-    <cfRule type="containsText" dxfId="31" priority="8" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="5" priority="8" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",V7)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="30" priority="9" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="4" priority="9" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",V7)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="V16:V17">
-    <cfRule type="containsText" dxfId="29" priority="6" operator="containsText" text="NO">
+    <cfRule type="containsText" dxfId="3" priority="6" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",V16)))</formula>
     </cfRule>
-    <cfRule type="containsText" dxfId="28" priority="7" operator="containsText" text="YES">
+    <cfRule type="containsText" dxfId="2" priority="7" operator="containsText" text="YES">
       <formula>NOT(ISERROR(SEARCH("YES",V16)))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="T1:T1048576">
-    <cfRule type="containsText" dxfId="2" priority="2" operator="containsText" text="YES">
-      <formula>NOT(ISERROR(SEARCH("YES",T1)))</formula>
-    </cfRule>
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="NO">
       <formula>NOT(ISERROR(SEARCH("NO",T1)))</formula>
+    </cfRule>
+    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="YES">
+      <formula>NOT(ISERROR(SEARCH("YES",T1)))</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -2883,7 +5152,7 @@
       </c>
       <c r="B3">
         <f>COUNTA(BENI_Data!D:D)-1</f>
-        <v>23</v>
+        <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
@@ -2892,7 +5161,7 @@
       </c>
       <c r="B4">
         <f>AVERAGE(BENI_Data!R:R)</f>
-        <v>6.6313816994128597E-2</v>
+        <v>8.6354187953737643E-2</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
